--- a/dataset/construct/dataset_splits/data_size/10_percent/lmu/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/lmu/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54246275</v>
+        <v>53203375</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,111 +625,114 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>83.29089664613279</v>
+        <v>77.06776180698149</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>31.1345807515033</v>
       </c>
       <c r="E2" t="n">
-        <v>25.1952632905014</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>55</v>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>803</v>
+      </c>
+      <c r="I2" t="n">
+        <v>270</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>346</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1419</v>
+      </c>
+      <c r="L2" t="n">
+        <v>408</v>
+      </c>
+      <c r="M2" t="n">
+        <v>147</v>
+      </c>
+      <c r="N2" t="n">
+        <v>126</v>
+      </c>
       <c r="O2" t="n">
-        <v>194</v>
+        <v>681</v>
       </c>
       <c r="P2" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>724</v>
+        <v>167</v>
       </c>
       <c r="S2" t="n">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>27.9</v>
       </c>
       <c r="V2" t="n">
-        <v>79</v>
+        <v>0.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>29.31634051752712</v>
       </c>
       <c r="X2" t="n">
-        <v>26.4</v>
+        <v>28.06240649728205</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>83.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>504.8</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>138</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>51375337</v>
+        <v>55005074</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -752,79 +740,77 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>81.3716632443532</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>90.03422313483919</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28.125</v>
+      </c>
       <c r="E3" t="n">
-        <v>25.3515413737155</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>55</v>
+      </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>55</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>840</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>611</v>
+        <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>483</v>
+        <v>79</v>
       </c>
       <c r="N3" t="n">
-        <v>1933</v>
+        <v>161</v>
       </c>
       <c r="O3" t="n">
-        <v>871</v>
+        <v>417</v>
       </c>
       <c r="P3" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>463</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1652</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>76</v>
+        <v>0.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>22.60000191904914</v>
       </c>
       <c r="X3" t="n">
-        <v>29.9</v>
+        <v>21.6401826367892</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>683.9</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -833,36 +819,27 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>207</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55330188</v>
+        <v>55845012</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -870,71 +847,77 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89.8097193702943</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>86.8665297741273</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25.9515570934256</v>
+      </c>
       <c r="E4" t="n">
-        <v>24.6530314097882</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>55</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>403.2898</v>
+      </c>
+      <c r="M4" t="n">
+        <v>269.92798</v>
+      </c>
+      <c r="N4" t="n">
+        <v>481.10962</v>
+      </c>
       <c r="O4" t="n">
-        <v>134</v>
+        <v>1154.3274</v>
       </c>
       <c r="P4" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>347</v>
+        <v>26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>23</v>
+        <v>18.405811</v>
       </c>
       <c r="V4" t="n">
-        <v>23</v>
+        <v>0.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>20.5505223365696</v>
       </c>
       <c r="X4" t="n">
-        <v>24.2</v>
+        <v>18.04414161374014</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>435.6</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -949,26 +932,21 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+        <v>144</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>52803803</v>
+        <v>54755591</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -976,73 +954,71 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87.45516769336071</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>71.5482546201232</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21.3333333333333</v>
+      </c>
       <c r="E5" t="n">
-        <v>19.2335607490202</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>55</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>134</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>311</v>
+        <v>109</v>
       </c>
       <c r="M5" t="n">
-        <v>315</v>
+        <v>65</v>
       </c>
       <c r="N5" t="n">
-        <v>760</v>
+        <v>78</v>
       </c>
       <c r="O5" t="n">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="P5" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>760</v>
+        <v>34</v>
       </c>
       <c r="S5" t="n">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>287</v>
+        <v>19.7</v>
       </c>
       <c r="V5" t="n">
-        <v>414</v>
+        <v>0.31</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>20.84929754503829</v>
       </c>
       <c r="X5" t="n">
-        <v>20.3</v>
+        <v>19.70629496237749</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>62.9</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>304.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1051,13 +1027,13 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1066,23 +1042,14 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54042809</v>
+        <v>53557204</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1090,65 +1057,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>78.88843258042441</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>86.97330595482551</v>
+      </c>
+      <c r="D6" t="n">
+        <v>26.2975778546713</v>
+      </c>
       <c r="E6" t="n">
-        <v>26.9274376417234</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33</v>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="I6" t="n">
+        <v>148</v>
+      </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="K6" t="n">
+        <v>275</v>
+      </c>
+      <c r="L6" t="n">
+        <v>67</v>
+      </c>
+      <c r="M6" t="n">
+        <v>123</v>
+      </c>
+      <c r="N6" t="n">
+        <v>60</v>
+      </c>
       <c r="O6" t="n">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>29.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>29.12535458581685</v>
       </c>
       <c r="X6" t="n">
-        <v>21.1</v>
+        <v>28.60168539601018</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>73.2</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>374.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1163,36 +1144,27 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>103</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>98</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>51489740</v>
+        <v>55663824</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1200,121 +1172,106 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>71.5263518138262</v>
+        <v>83.5154004106776</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>23.1836734693878</v>
       </c>
       <c r="E7" t="n">
-        <v>37.8328741965106</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>331</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>1221.1014</v>
       </c>
       <c r="M7" t="n">
-        <v>93</v>
+        <v>1135.735</v>
       </c>
       <c r="N7" t="n">
-        <v>440</v>
+        <v>912.9004</v>
       </c>
       <c r="O7" t="n">
-        <v>331</v>
+        <v>3269.7368</v>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>28.412994</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>30.40101774202542</v>
       </c>
       <c r="X7" t="n">
-        <v>22.8</v>
+        <v>29.19972005951999</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>72.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>398.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54731359</v>
+        <v>52794228</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1322,65 +1279,79 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.6714579055441</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>85.8261464750171</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24.4351866688031</v>
+      </c>
       <c r="E8" t="n">
-        <v>26.8135904499541</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>174</v>
+      </c>
+      <c r="I8" t="n">
+        <v>523</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>325</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L8" t="n">
+        <v>136</v>
+      </c>
+      <c r="M8" t="n">
+        <v>198</v>
+      </c>
+      <c r="N8" t="n">
+        <v>120</v>
+      </c>
       <c r="O8" t="n">
-        <v>118</v>
+        <v>454</v>
       </c>
       <c r="P8" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>22.02704412391832</v>
       </c>
       <c r="X8" t="n">
-        <v>21.8</v>
+        <v>21.32308236219442</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>385.7</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1395,32 +1366,23 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53410846</v>
+        <v>54155745</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1428,82 +1390,80 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>77.03490759753591</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>87.41957563312801</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.9896193771626</v>
+      </c>
       <c r="E9" t="n">
-        <v>32.8768872290849</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48</v>
+      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>901</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>870</v>
+        <v>390</v>
       </c>
       <c r="M9" t="n">
-        <v>678</v>
+        <v>255</v>
       </c>
       <c r="N9" t="n">
-        <v>2449</v>
+        <v>251</v>
       </c>
       <c r="O9" t="n">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="P9" t="n">
-        <v>763</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2333</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>29.06169260858009</v>
       </c>
       <c r="X9" t="n">
-        <v>28.9</v>
+        <v>28.76149739172902</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>97.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>705.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1521,20 +1481,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55088684</v>
+        <v>54564507</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1542,109 +1497,102 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69.7768651608487</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>73.9794661190965</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30.8979120501857</v>
+      </c>
       <c r="E10" t="n">
-        <v>25.3515413737155</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>312</v>
+      </c>
+      <c r="M10" t="n">
+        <v>251</v>
+      </c>
+      <c r="N10" t="n">
+        <v>283</v>
+      </c>
       <c r="O10" t="n">
-        <v>153</v>
+        <v>846</v>
       </c>
       <c r="P10" t="n">
-        <v>213</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>28.1385939386471</v>
       </c>
       <c r="X10" t="n">
-        <v>24.3</v>
+        <v>26.64982210171906</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>455.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>154</v>
-      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53628169</v>
+        <v>53708820</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1652,87 +1600,91 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86.7077344284736</v>
+        <v>83.70157426420261</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>28.6501377410468</v>
       </c>
       <c r="E11" t="n">
-        <v>23.6614386154678</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>55</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="I11" t="n">
+        <v>251</v>
+      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="K11" t="n">
-        <v>577</v>
+        <v>376</v>
       </c>
       <c r="L11" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="N11" t="n">
-        <v>1234</v>
+        <v>62</v>
       </c>
       <c r="O11" t="n">
-        <v>577</v>
+        <v>363</v>
       </c>
       <c r="P11" t="n">
-        <v>380</v>
+        <v>337</v>
       </c>
       <c r="Q11" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1234</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>31.54450972081365</v>
       </c>
       <c r="X11" t="n">
-        <v>27.5</v>
+        <v>30.4829496562869</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>87.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>580.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1747,24 +1699,15 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>233</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>259</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>52277005</v>
+        <v>54246275</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1772,86 +1715,80 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>77.4811772758385</v>
+        <v>83.29089664613279</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>25.1952632905014</v>
       </c>
       <c r="E12" t="n">
-        <v>28.515625</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>38</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>214</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M12" t="n">
-        <v>101</v>
+        <v>295</v>
       </c>
       <c r="N12" t="n">
-        <v>514</v>
+        <v>235</v>
       </c>
       <c r="O12" t="n">
-        <v>75</v>
+        <v>724</v>
       </c>
       <c r="P12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>26.70619945082004</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>25.3521463032681</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>79.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>478.1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1863,26 +1800,21 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+        <v>138</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>53896292</v>
+        <v>54108010</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1890,76 +1822,80 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>73.35249828884329</v>
+        <v>87.4715947980835</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>23.4375</v>
       </c>
       <c r="E13" t="n">
-        <v>28.4090909090909</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>120</v>
+      </c>
+      <c r="M13" t="n">
+        <v>243</v>
+      </c>
+      <c r="N13" t="n">
+        <v>197</v>
+      </c>
       <c r="O13" t="n">
-        <v>392</v>
+        <v>560</v>
       </c>
       <c r="P13" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>563</v>
+        <v>114</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>25.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>25.91042473536056</v>
       </c>
       <c r="X13" t="n">
-        <v>26.1</v>
+        <v>24.57173563494069</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>83.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1977,24 +1913,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>198</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55509378</v>
+        <v>53336242</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2002,65 +1929,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>72.13689253935659</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>88.2847364818617</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25.3515413737155</v>
+      </c>
       <c r="E14" t="n">
-        <v>31.8877551020408</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>298</v>
+      </c>
+      <c r="I14" t="n">
+        <v>337</v>
+      </c>
       <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>720</v>
+      </c>
+      <c r="L14" t="n">
+        <v>298</v>
+      </c>
+      <c r="M14" t="n">
+        <v>337</v>
+      </c>
+      <c r="N14" t="n">
+        <v>85</v>
+      </c>
       <c r="O14" t="n">
-        <v>338.7251</v>
+        <v>720</v>
       </c>
       <c r="P14" t="n">
-        <v>281.04163</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>210.4855</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>830.2523</v>
+        <v>245</v>
       </c>
       <c r="S14" t="n">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="V14" t="n">
-        <v>82</v>
+        <v>0.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>29.47549546061902</v>
       </c>
       <c r="X14" t="n">
-        <v>21.628544</v>
+        <v>28.34231516255181</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>78.25157</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>414.7697</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2069,42 +2010,33 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>158</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>135</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55673806</v>
+        <v>52110246</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2112,65 +2044,71 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>86.43942505133469</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>73.71937029431901</v>
+      </c>
+      <c r="D15" t="n">
+        <v>21.0667432730058</v>
+      </c>
       <c r="E15" t="n">
-        <v>20.7756232686981</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>335.40356</v>
+      </c>
+      <c r="M15" t="n">
+        <v>299.01544</v>
+      </c>
+      <c r="N15" t="n">
+        <v>159.00027</v>
+      </c>
       <c r="O15" t="n">
-        <v>308.5249</v>
+        <v>793.4192700000001</v>
       </c>
       <c r="P15" t="n">
-        <v>133.09209</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>279.9523</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>721.56934</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>25.28954</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>0.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>25.47957957201535</v>
       </c>
       <c r="X15" t="n">
-        <v>21.991661</v>
+        <v>24.61034541753594</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>75.75961</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>413.37274</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2179,37 +2117,28 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>196</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>188</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
